--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250611134353</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-11T13:43:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134353</t>
+    <t>20250616134739</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:53+01:00</t>
+    <t>2025-06-16T13:47:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -170,7 +170,7 @@
     <t>419620001</t>
   </si>
   <si>
-    <t>mort</t>
+    <t>décès</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -146,6 +146,21 @@
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
   <si>
+    <t>160849004</t>
+  </si>
+  <si>
+    <t>retour au domicile</t>
+  </si>
+  <si>
+    <t>419620001</t>
+  </si>
+  <si>
+    <t>décès</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>127</t>
   </si>
   <si>
@@ -158,22 +173,7 @@
     <t>Etablissement d'hébergement pour personnes âgées dépendantes</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R66-CategorieEtablissement/FHIR/TRE-R66-CategorieEtablissement</t>
-  </si>
-  <si>
-    <t>160849004</t>
-  </si>
-  <si>
-    <t>retour au domicile</t>
-  </si>
-  <si>
-    <t>419620001</t>
-  </si>
-  <si>
-    <t>décès</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice</t>
   </si>
 </sst>
 </file>

--- a/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-mode-sortie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
